--- a/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
   <si>
     <t>JOBY</t>
   </si>
@@ -656,82 +656,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -744,31 +744,34 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="D8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -803,13 +806,16 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>200</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>3</v>
@@ -862,13 +868,16 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>800</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>3</v>
@@ -921,8 +930,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -944,50 +956,51 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>102100</v>
+      </c>
+      <c r="E12" s="3">
         <v>100600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>88800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>75500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>76100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>73900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>74200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>72100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>57300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>52100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>54000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>34200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>31800</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1003,8 +1016,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1062,13 +1078,16 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1076,35 +1095,35 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9700</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1112,8 +1131,8 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1121,8 +1140,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1180,8 +1202,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1200,53 +1225,54 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>129300</v>
+      </c>
+      <c r="E17" s="3">
         <v>128200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>116000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>99700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>101400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>97100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>99400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>94300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>77300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>77400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>68400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>45800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>40200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,53 +1285,56 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-116000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-99700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-101400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-97100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-99400</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3">
+        <v>-128300</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>-94300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-77300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-77400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-68400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-45800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-40200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,8 +1347,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1341,52 +1373,53 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-170100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-13600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>34500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>18000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>49900</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>32100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>71800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1400,50 +1433,53 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-278600</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-106300</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-60300</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-72800</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-43700</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3">
+        <v>-106900</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>-57100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-74200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-60000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-37300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-31600</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,8 +1495,11 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1473,8 +1512,8 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1489,28 +1528,28 @@
         <v>0</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1518,53 +1557,56 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-115100</v>
+      </c>
+      <c r="E23" s="3">
         <v>1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-286000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-113400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-66900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-79200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-49500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-62300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-78900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-65000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-41500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-33900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,8 +1619,11 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1586,17 +1631,17 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -1604,11 +1649,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-10500</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1618,8 +1663,8 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
@@ -1627,8 +1672,8 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1636,8 +1681,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1695,53 +1743,56 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-115100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-286100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-113400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-66900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-79200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-49600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-62300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-78900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-65000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-41500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-33900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,53 +1805,56 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-115100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-286100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-113400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-66900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-79200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-49600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-62300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-78900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-65000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-41500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-33900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1813,8 +1867,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1872,8 +1929,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1931,8 +1991,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1990,8 +2053,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2049,52 +2115,55 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
-        <v>170100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>13600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-34500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-18000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-49900</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-32100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-71800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2108,53 +2177,56 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-115100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-286100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-113400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-66900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-79200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-49600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-62300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-78900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-65000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-41500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-33900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,8 +2239,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2226,53 +2301,56 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-115100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-286100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-113400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-66900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-79200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-49600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-62300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-78900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-65000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-41500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-33900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,58 +2363,61 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2349,8 +2430,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2372,8 +2456,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2395,53 +2480,54 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E41" s="3">
         <v>480400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>382700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>49800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>146100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>193800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>311100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>417100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>955600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1016500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>44300</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3">
         <v>2800</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2454,44 +2540,47 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>828200</v>
+      </c>
+      <c r="E42" s="3">
         <v>632100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>812100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>928000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>910700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>880700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>840400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>803700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>343200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>346000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>375200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2504,8 +2593,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2513,44 +2602,47 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E43" s="3">
         <v>6900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3900</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2563,8 +2655,8 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -2572,8 +2664,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2631,53 +2726,56 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E45" s="3">
         <v>18700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>23400</v>
       </c>
       <c r="H45" s="3">
         <v>23400</v>
       </c>
       <c r="I45" s="3">
+        <v>23400</v>
+      </c>
+      <c r="J45" s="3">
         <v>21900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>19100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>17400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>17600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,53 +2788,56 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1055800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1138200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1224800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1013100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1084200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1104000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1177600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1242600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1318500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1382500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>430500</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3">
         <v>3800</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2749,13 +2850,16 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>59600</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -2763,39 +2867,39 @@
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
         <v>72100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>27000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>690000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2808,44 +2912,47 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>131700</v>
+      </c>
+      <c r="E48" s="3">
         <v>128100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>116500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>117100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>117300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>63000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>61000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>57900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>53200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>41600</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2965,8 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -2867,44 +2974,47 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E49" s="3">
         <v>22000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>23600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>25100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>26600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>28200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>29600</v>
-      </c>
-      <c r="J49" s="3">
-        <v>25300</v>
       </c>
       <c r="K49" s="3">
         <v>25300</v>
       </c>
       <c r="L49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="M49" s="3">
         <v>18700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19700</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2917,8 +3027,8 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -2926,8 +3036,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2985,8 +3098,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3044,44 +3160,47 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E52" s="3">
         <v>61300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>61900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>63400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>65000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>68000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>70500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>71100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>66600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>61300</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3094,8 +3213,8 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -3103,8 +3222,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3162,53 +3284,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1269400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1349600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1426700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1218700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1293000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1273800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1356300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1423300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1488400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1532000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>566100</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3">
         <v>693700</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,8 +3346,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3244,8 +3372,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3267,53 +3396,54 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
-      </c>
-      <c r="K57" s="3">
-        <v>3600</v>
       </c>
       <c r="L57" s="3">
         <v>3600</v>
       </c>
       <c r="M57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="N57" s="3">
         <v>5500</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3">
         <v>700</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,16 +3456,19 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -3343,27 +3476,27 @@
       <c r="G58" s="3">
         <v>0</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>700</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3376,8 +3509,8 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -3385,53 +3518,56 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E59" s="3">
         <v>45200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>40000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>26400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>28100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>300</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,53 +3580,56 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E60" s="3">
         <v>50000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>44100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12400</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3">
         <v>1100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3503,8 +3642,11 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3530,17 +3672,17 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>1400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>78600</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3562,53 +3704,56 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>189900</v>
+      </c>
+      <c r="E62" s="3">
         <v>190300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>298100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>118900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>98000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>84900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>97700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>140700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>156400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>218200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2800</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>24400</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,8 +3766,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3680,8 +3828,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3739,8 +3890,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3798,53 +3952,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>235100</v>
+      </c>
+      <c r="E66" s="3">
         <v>240300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>342200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>149200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>128200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>113700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>127700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>158900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>171600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>227300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>93800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3">
         <v>25400</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3857,8 +4014,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3880,8 +4040,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3939,8 +4100,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3998,8 +4162,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4031,11 +4198,11 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>845900</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -4057,8 +4224,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4116,53 +4286,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1247700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1132600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1134100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-848000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-734700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-667700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-588500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-538900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-476600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-481700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-402800</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-200</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4175,8 +4348,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4234,8 +4410,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4293,8 +4472,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4352,53 +4534,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1034400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1109300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1084600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1069500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1164700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1160200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1228700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1264400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1316800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1304700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-373700</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3">
         <v>668300</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4411,8 +4596,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4470,58 +4658,61 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4534,53 +4725,56 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-115100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-286100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-113400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-66900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-79200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-49600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-62300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-78900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-65000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-41500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-33900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4593,8 +4787,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4616,55 +4813,56 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E83" s="3">
         <v>7800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2200</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -4675,8 +4873,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4734,8 +4935,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4793,8 +4997,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4852,8 +5059,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4911,8 +5121,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4970,53 +5183,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-83300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-80200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-71700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-78600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-53100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-68300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-53100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-61400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-48700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-69500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-47900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-29700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-30300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5029,8 +5245,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5052,55 +5271,56 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-30500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5600</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -5111,8 +5331,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5170,8 +5393,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5229,53 +5455,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-196400</v>
+      </c>
+      <c r="E94" s="3">
         <v>177900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>117900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-54800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-49100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-50700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-476100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>21600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>42800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-690000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5288,8 +5517,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5311,8 +5543,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5370,8 +5603,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5429,8 +5665,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5488,8 +5727,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5547,53 +5789,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>284500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>60200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1020100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>75000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>693300</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5606,8 +5851,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5665,53 +5913,56 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-276400</v>
+      </c>
+      <c r="E102" s="3">
         <v>97700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>330600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-97300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-47700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-117200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-103800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-537500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-60900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>972200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-72400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>39400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>12600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2800</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5722,6 +5973,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="92">
   <si>
     <t>JOBY</t>
   </si>
@@ -656,85 +656,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -747,17 +748,20 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>1000</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
@@ -773,8 +777,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -809,17 +813,20 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
         <v>200</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
       </c>
@@ -871,17 +878,20 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
         <v>800</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
       </c>
@@ -933,8 +943,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,53 +970,54 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E12" s="3">
         <v>102100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>100600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>88800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>75500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>76100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>73900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>74200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>72100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>57300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>52100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>54000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>34200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>31800</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1019,8 +1033,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1081,16 +1098,19 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1098,35 +1118,35 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
@@ -1134,8 +1154,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1143,8 +1163,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1205,8 +1228,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1226,56 +1252,57 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>145900</v>
+      </c>
+      <c r="E17" s="3">
         <v>129300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>128200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>116000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>99700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>101400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>97100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>99400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>94300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>77300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>77400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>68400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>45800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1288,17 +1315,20 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-128300</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,30 +1344,30 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>-94300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-77300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-77400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-68400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-45800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,8 +1380,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1374,17 +1407,18 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>13200</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1400,29 +1434,29 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>32100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>71800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6300</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1436,17 +1470,20 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>-106900</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1462,27 +1499,27 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-57100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-74200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-60000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-37300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-31600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,8 +1535,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1515,8 +1555,8 @@
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1531,28 +1571,28 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1560,56 +1600,59 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-94600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-115100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-286000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-113400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-66900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-79200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-49500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-62300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-78900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-65000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-41500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-33900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1622,8 +1665,11 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1634,17 +1680,17 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1652,11 +1698,11 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-10500</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1666,8 +1712,8 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -1675,8 +1721,8 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1684,8 +1730,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1746,56 +1795,59 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-94600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-115100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-286100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-113400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-66900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-79200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-49600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-62300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-78900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-65000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-41500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-33900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,56 +1860,59 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-94600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-115100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-286100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-113400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-66900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-79200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-49600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-62300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-78900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-65000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-41500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-33900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1870,8 +1925,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1932,8 +1990,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1994,8 +2055,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2056,8 +2120,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2118,17 +2185,20 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-13200</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2144,29 +2214,29 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-32100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-71800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -2180,56 +2250,59 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-94600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-115100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-286100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-113400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-66900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-79200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-49600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-62300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-78900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-65000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-41500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-33900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2242,8 +2315,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2304,56 +2380,59 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-94600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-115100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-286100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-113400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-66900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-79200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-49600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-62300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-78900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-65000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-41500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-33900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,61 +2445,64 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2515,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2457,8 +2542,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2481,56 +2567,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>110500</v>
+      </c>
+      <c r="E41" s="3">
         <v>204000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>480400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>382700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>146100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>193800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>311100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>417100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>955600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1016500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>44300</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3">
         <v>2800</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,47 +2630,50 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>813300</v>
+      </c>
+      <c r="E42" s="3">
         <v>828200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>632100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>812100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>928000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>910700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>880700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>840400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>803700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>343200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>346000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>375200</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2596,8 +2686,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2605,47 +2695,50 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E43" s="3">
         <v>4700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3900</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2658,8 +2751,8 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -2667,8 +2760,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2729,56 +2825,59 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E45" s="3">
         <v>18800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>24500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>23400</v>
       </c>
       <c r="I45" s="3">
         <v>23400</v>
       </c>
       <c r="J45" s="3">
+        <v>23400</v>
+      </c>
+      <c r="K45" s="3">
         <v>21900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>17400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7100</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,56 +2890,59 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>951700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1055800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1138200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1224800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1013100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1084200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1104000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1177600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1242600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1318500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1382500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>430500</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3">
         <v>3800</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,16 +2955,19 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>59600</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
+      <c r="E47" s="3">
+        <v>59600</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -2870,39 +2975,39 @@
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
-        <v>0</v>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
         <v>72100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>20100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>27000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>690000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2915,47 +3020,50 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>132200</v>
+      </c>
+      <c r="E48" s="3">
         <v>131700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>128100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>116500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>117100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>117300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>63000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>61000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>57900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>53200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>41600</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2968,8 +3076,8 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -2977,47 +3085,50 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E49" s="3">
         <v>20600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>23600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>25100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>26600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>28200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>29600</v>
-      </c>
-      <c r="K49" s="3">
-        <v>25300</v>
       </c>
       <c r="L49" s="3">
         <v>25300</v>
       </c>
       <c r="M49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="N49" s="3">
         <v>18700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>19700</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3030,8 +3141,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3039,8 +3150,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3101,8 +3215,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3163,8 +3280,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3172,38 +3292,38 @@
         <v>1800</v>
       </c>
       <c r="E52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F52" s="3">
         <v>61300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>61900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>63400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>65000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>68000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>70500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>71100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>66600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>61300</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3216,8 +3336,8 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3225,8 +3345,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3287,56 +3410,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1164400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1269400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1349600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1426700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1218700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1293000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1273800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1356300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1423300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1488400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1532000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>566100</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3">
         <v>693700</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3475,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3373,8 +3502,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3397,56 +3527,57 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>3600</v>
       </c>
       <c r="M57" s="3">
         <v>3600</v>
       </c>
       <c r="N57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="O57" s="3">
         <v>5500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3459,8 +3590,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3485,21 +3619,21 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>700</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3512,8 +3646,8 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -3521,56 +3655,59 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E59" s="3">
         <v>42100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>45200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>40000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>28100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6200</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>300</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3583,56 +3720,59 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E60" s="3">
         <v>45100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>50000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>44100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>30200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12400</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3">
         <v>1100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3785,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3675,17 +3818,17 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>1400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>78600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3707,56 +3850,59 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E62" s="3">
         <v>189900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>190300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>298100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>118900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>98000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>84900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>97700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>140700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>156400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>218200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2800</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
         <v>24400</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3769,8 +3915,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3831,8 +3980,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3893,8 +4045,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3955,56 +4110,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>189200</v>
+      </c>
+      <c r="E66" s="3">
         <v>235100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>240300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>342200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>149200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>128200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>113700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>127700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>158900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>171600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>227300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>93800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3">
         <v>25400</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4017,8 +4175,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4041,8 +4202,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4103,8 +4265,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4165,8 +4330,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4201,11 +4369,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>845900</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -4227,8 +4395,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4289,56 +4460,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1342300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1247700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1132600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1134100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-848000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-734700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-667700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-588500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-538900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-476600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-481700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-402800</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3">
         <v>-200</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4351,8 +4525,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4413,8 +4590,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4475,8 +4655,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4537,56 +4720,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>975100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1034400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1109300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1084600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1069500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1164700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1160200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1228700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1264400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1316800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1304700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-373700</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3">
         <v>668300</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4599,8 +4785,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4661,61 +4850,64 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4728,56 +4920,59 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-94600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-115100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-286100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-113400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-66900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-79200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-49600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-62300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-78900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-65000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-41500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-33900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4985,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4814,58 +5012,59 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E83" s="3">
         <v>8100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2200</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -4876,8 +5075,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4938,8 +5140,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5000,8 +5205,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5062,8 +5270,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5124,8 +5335,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5186,56 +5400,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-106600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-83300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-80200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-71700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-78600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-53100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-68300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-53100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-61400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-48700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-69500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-47900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-29700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-30300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5248,8 +5465,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5272,58 +5492,59 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-30500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -5334,8 +5555,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5396,8 +5620,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5458,56 +5685,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-196400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>177900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>117900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-54800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-49100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-50700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-476100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>21600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>42800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-690000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5520,8 +5750,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5544,8 +5777,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5606,8 +5840,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5668,8 +5905,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5730,8 +5970,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,56 +6035,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>500</v>
+      </c>
+      <c r="E100" s="3">
         <v>3400</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>284500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>60200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1020100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>75000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>693300</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5854,8 +6100,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5916,56 +6165,59 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-93500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-276400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>97700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>330600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-97300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-47700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-117200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-103800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-537500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-60900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>972200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-72400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>39400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2800</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5976,6 +6228,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
   <si>
     <t>JOBY</t>
   </si>
@@ -656,89 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -751,8 +752,11 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -760,11 +764,11 @@
         <v>3</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>1000</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
@@ -780,8 +784,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -816,8 +820,11 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -825,11 +832,11 @@
         <v>0</v>
       </c>
       <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <v>200</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
       </c>
@@ -881,8 +888,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -890,11 +900,11 @@
         <v>3</v>
       </c>
       <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>800</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
       </c>
@@ -946,8 +956,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -971,56 +984,57 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E12" s="3">
         <v>115600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>102100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>100600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>88800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>75500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>76100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>73900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>74200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>72100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>57300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>52100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>54000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>34200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>31800</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1036,8 +1050,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1101,19 +1118,22 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -1121,35 +1141,35 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9700</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
@@ -1157,8 +1177,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1166,8 +1186,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1231,8 +1254,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1253,59 +1279,60 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>144300</v>
+      </c>
+      <c r="E17" s="3">
         <v>145900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>129300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>128200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>116000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>99700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>101400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>97100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>99400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>94300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>77300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>77400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>68400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>45800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>40200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>200</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,8 +1345,11 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1327,11 +1357,11 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-145900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-128300</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1347,30 +1377,30 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>-94300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-77300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-77400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-68400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-40200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1383,8 +1413,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1408,8 +1441,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1417,11 +1451,11 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>51400</v>
+      </c>
+      <c r="F20" s="3">
         <v>13200</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1437,29 +1471,29 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>32100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>71800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1473,8 +1507,11 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1482,11 +1519,11 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-106900</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1502,27 +1539,27 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-57100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-74200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-60000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-37300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-31600</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1538,8 +1575,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1558,8 +1598,8 @@
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1574,28 +1614,28 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1603,59 +1643,62 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-123300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-94600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-115100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-286000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-113400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-66900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-79200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-49500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-62300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-78900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-65000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-41500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-33900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1668,8 +1711,11 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1683,17 +1729,17 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1701,11 +1747,11 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-10500</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1715,8 +1761,8 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
@@ -1724,8 +1770,8 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1733,8 +1779,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1798,59 +1847,62 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-123300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-94600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-115100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-286100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-113400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-66900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-79200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-49600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-62300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-78900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-65000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-41500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-33900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1863,59 +1915,62 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-123300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-94600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-115100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-286100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-113400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-66900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-79200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-49600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-62300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-78900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-65000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-41500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-33900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1928,8 +1983,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1993,8 +2051,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2058,8 +2119,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2123,8 +2187,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2188,8 +2255,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2197,11 +2267,11 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-51400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-13200</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2217,29 +2287,29 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-32100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-71800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2253,59 +2323,62 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-123300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-94600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-115100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-286100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-113400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-66900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-79200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-49600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-62300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-78900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-65000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-41500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-33900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2318,8 +2391,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2383,59 +2459,62 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-123300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-94600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-115100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-286100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-113400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-66900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-79200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-49600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-62300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-78900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-65000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-41500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-33900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2448,64 +2527,67 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2518,8 +2600,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2543,8 +2628,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2568,59 +2654,60 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>175100</v>
+      </c>
+      <c r="E41" s="3">
         <v>110500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>204000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>480400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>382700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>146100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>193800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>311100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>417100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>955600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1016500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44300</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3">
         <v>2800</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2633,50 +2720,53 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>649900</v>
+      </c>
+      <c r="E42" s="3">
         <v>813300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>828200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>632100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>812100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>928000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>910700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>880700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>840400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>803700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>343200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>346000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>375200</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2689,8 +2779,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2698,50 +2788,53 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E43" s="3">
         <v>6900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3900</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2754,8 +2847,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2763,8 +2856,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2828,59 +2924,62 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E45" s="3">
         <v>20900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>20300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>24500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>23400</v>
       </c>
       <c r="J45" s="3">
         <v>23400</v>
       </c>
       <c r="K45" s="3">
+        <v>23400</v>
+      </c>
+      <c r="L45" s="3">
         <v>21900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7100</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3">
         <v>1000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2893,59 +2992,62 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>857700</v>
+      </c>
+      <c r="E46" s="3">
         <v>951700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1055800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1138200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1224800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1013100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1084200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1104000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1177600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1242600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1318500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1382500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>430500</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3">
         <v>3800</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2958,8 +3060,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2969,8 +3074,8 @@
       <c r="E47" s="3">
         <v>59600</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
+      <c r="F47" s="3">
+        <v>59600</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -2978,39 +3083,39 @@
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
-        <v>0</v>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
         <v>72100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>27000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>690000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3023,50 +3128,53 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>133500</v>
+      </c>
+      <c r="E48" s="3">
         <v>132200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>131700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>128100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>116500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>117100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>117300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>63000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>61000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>57900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>53200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>44000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>41600</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3079,8 +3187,8 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3088,50 +3196,53 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E49" s="3">
         <v>19000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>25100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>26600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>28200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29600</v>
-      </c>
-      <c r="L49" s="3">
-        <v>25300</v>
       </c>
       <c r="M49" s="3">
         <v>25300</v>
       </c>
       <c r="N49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="O49" s="3">
         <v>18700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19700</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3144,8 +3255,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3153,8 +3264,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3218,8 +3332,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3283,8 +3400,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3295,38 +3415,38 @@
         <v>1800</v>
       </c>
       <c r="F52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G52" s="3">
         <v>61300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>61900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>63400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>65000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>68000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>70500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>71100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>66600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>61300</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3339,8 +3459,8 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3348,8 +3468,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3413,59 +3536,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1077800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1164400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1269400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1349600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1426700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1218700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1293000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1273800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1356300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1423300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1488400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1532000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>566100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3">
         <v>693700</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3478,8 +3604,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3503,8 +3632,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3528,59 +3658,60 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E57" s="3">
         <v>3700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2700</v>
-      </c>
-      <c r="M57" s="3">
-        <v>3600</v>
       </c>
       <c r="N57" s="3">
         <v>3600</v>
       </c>
       <c r="O57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="P57" s="3">
         <v>5500</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3">
         <v>700</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3593,8 +3724,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3622,21 +3756,21 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>700</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3649,8 +3783,8 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3658,59 +3792,62 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E59" s="3">
         <v>34500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>45200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>40000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>28100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6200</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3">
         <v>300</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,59 +3860,62 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E60" s="3">
         <v>38200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>45100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>50000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>44100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>30300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12400</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3">
         <v>1100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3788,8 +3928,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3821,17 +3964,17 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>1400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>78600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3853,59 +3996,62 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>140100</v>
+      </c>
+      <c r="E62" s="3">
         <v>151000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>189900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>190300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>298100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>118900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>98000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>84900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>97700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>140700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>156400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>218200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2800</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3">
         <v>24400</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3918,8 +4064,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3983,8 +4132,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4048,8 +4200,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4113,59 +4268,62 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>183200</v>
+      </c>
+      <c r="E66" s="3">
         <v>189200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>235100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>240300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>342200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>149200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>128200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>113700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>127700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>158900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>171600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>227300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>93800</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3">
         <v>25400</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4336,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4203,8 +4364,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4268,8 +4430,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4333,8 +4498,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4372,11 +4540,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>845900</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4398,8 +4566,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4463,59 +4634,62 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1465600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1342300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1247700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1132600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1134100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-848000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-734700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-667700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-588500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-538900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-476600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-481700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-402800</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3">
         <v>-200</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4528,8 +4702,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4593,8 +4770,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4658,8 +4838,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4723,59 +4906,62 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>894600</v>
+      </c>
+      <c r="E76" s="3">
         <v>975100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1034400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1109300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1084600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1069500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1164700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1160200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1228700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1264400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1316800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1304700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-373700</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3">
         <v>668300</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4788,8 +4974,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4853,64 +5042,67 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4923,59 +5115,62 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-123300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-94600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-115100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-286100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-113400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-66900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-79200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-49600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-62300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-78900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-65000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-41500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-33900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4988,8 +5183,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5013,61 +5211,62 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E83" s="3">
         <v>8500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2200</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -5078,8 +5277,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5143,8 +5345,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5208,8 +5413,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5273,8 +5481,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5338,8 +5549,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5403,59 +5617,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-98800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-106600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-83300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-80200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-71700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-78600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-53100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-68300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-53100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-61400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-48700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-69500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-47900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-29700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-30300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,8 +5685,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5493,61 +5713,62 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5600</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5558,8 +5779,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5623,8 +5847,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5688,59 +5915,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>158600</v>
+      </c>
+      <c r="E94" s="3">
         <v>12600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-196400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>177900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>117900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-54800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-49100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-50700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-476100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>21600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-23100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>42800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-690000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5753,8 +5983,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5778,8 +6011,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5843,8 +6077,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5908,8 +6145,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5973,8 +6213,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6038,59 +6281,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3400</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>284500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>60200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1020100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>75000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>693300</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6103,8 +6349,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6168,59 +6417,62 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-93500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-276400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>97700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>330600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-97300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-47700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-117200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-103800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-537500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-60900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>972200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-72400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>39400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>12600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2800</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6231,6 +6483,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="92">
   <si>
     <t>JOBY</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -755,8 +756,11 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -767,11 +771,11 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>1000</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -787,8 +791,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -823,8 +827,11 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -835,11 +842,11 @@
         <v>0</v>
       </c>
       <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
         <v>200</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -891,23 +898,26 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>0</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
       </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
         <v>800</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,8 +969,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,59 +998,60 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>126100</v>
+      </c>
+      <c r="E12" s="3">
         <v>113000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>115600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>102100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>100600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>88800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>75500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>76100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>73900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>74200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>72100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>57300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>52100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>54000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>34200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>31800</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1067,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,8 +1138,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1132,11 +1152,11 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
+        <v>51900</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1144,35 +1164,35 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9700</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
@@ -1180,8 +1200,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1189,31 +1209,34 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>8900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1257,8 +1280,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,62 +1306,63 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>156700</v>
+      </c>
+      <c r="E17" s="3">
         <v>144300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>145900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>129300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>128200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>116000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>99700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>101400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>97100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>99400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>94300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>77300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>77400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>68400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>45800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>40200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>200</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,31 +1375,34 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-156700</v>
       </c>
       <c r="E18" s="3">
+        <v>-144300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-145900</v>
       </c>
-      <c r="F18" s="3">
-        <v>-128300</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+      <c r="G18" s="3">
+        <v>-128200</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-128200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-99700</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1380,30 +1410,30 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-94300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-77300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-77400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-68400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-45800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-40200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1446,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,31 +1475,32 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-3800</v>
       </c>
       <c r="E20" s="3">
-        <v>51400</v>
+        <v>-9800</v>
       </c>
       <c r="F20" s="3">
-        <v>13200</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>-39000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-52200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-116100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>180700</v>
+      </c>
+      <c r="J20" s="3">
+        <v>22000</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1474,29 +1508,29 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>32100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>71800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1510,31 +1544,34 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-144000</v>
       </c>
       <c r="E21" s="3">
-        <v>-86000</v>
+        <v>-125800</v>
       </c>
       <c r="F21" s="3">
-        <v>-106900</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-98400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-67900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-289200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-114700</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1542,27 +1579,27 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-57100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-74200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-37300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-31600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,8 +1615,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1601,8 +1641,8 @@
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1617,28 +1657,28 @@
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1646,62 +1686,65 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-143300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-123300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-94600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-115100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-286000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-113400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-66900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-79200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-49500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-62300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-78900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-65000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-41500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-33900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,13 +1757,16 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1732,17 +1778,17 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1750,11 +1796,11 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-10500</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1764,8 +1810,8 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
@@ -1773,8 +1819,8 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1782,8 +1828,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,62 +1899,65 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-143900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-123300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-94600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-115100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-286100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-113400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-66900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-79200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-49600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-62300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-78900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-65000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-41500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-33900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,62 +1970,65 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-143900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-123300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-94600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-115100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-286100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-113400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-66900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-79200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-49600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-62300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-78900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-65000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-41500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-33900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1986,8 +2041,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,8 +2112,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2122,8 +2183,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2254,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,31 +2325,34 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>3800</v>
       </c>
       <c r="E32" s="3">
-        <v>-51400</v>
+        <v>9800</v>
       </c>
       <c r="F32" s="3">
-        <v>-13200</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>39000</v>
+      </c>
+      <c r="G32" s="3">
+        <v>52200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>116100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-180700</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-22000</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -2290,29 +2360,29 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>-32100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-71800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2326,62 +2396,65 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-143900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-123300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-94600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-115100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-286100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-113400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-66900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-79200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-49600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-62300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-78900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-65000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-41500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-33900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2394,8 +2467,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,62 +2538,65 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-143900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-123300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-94600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-115100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-286100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-113400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-66900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-79200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-49600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-62300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-78900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-65000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-41500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-33900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2530,67 +2609,70 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2603,8 +2685,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2714,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,62 +2741,63 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>152300</v>
+      </c>
+      <c r="E41" s="3">
         <v>175100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>110500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>204000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>480400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>382700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>146100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>193800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>311100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>417100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>955600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1016500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>44300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3">
         <v>2800</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2723,53 +2810,56 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>557700</v>
+      </c>
+      <c r="E42" s="3">
         <v>649900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>813300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>828200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>632100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>812100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>928000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>910700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>880700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>840400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>803700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>343200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>346000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>375200</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2782,8 +2872,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2791,53 +2881,56 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E43" s="3">
         <v>13300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3900</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2850,8 +2943,8 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -2859,31 +2952,34 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2927,62 +3023,65 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>19400</v>
+        <v>11200</v>
       </c>
       <c r="E45" s="3">
-        <v>20900</v>
+        <v>16800</v>
       </c>
       <c r="F45" s="3">
-        <v>18800</v>
+        <v>14800</v>
       </c>
       <c r="G45" s="3">
-        <v>18700</v>
+        <v>11000</v>
       </c>
       <c r="H45" s="3">
-        <v>20300</v>
+        <v>11700</v>
       </c>
       <c r="I45" s="3">
-        <v>24500</v>
+        <v>13000</v>
       </c>
       <c r="J45" s="3">
-        <v>23400</v>
+        <v>12500</v>
       </c>
       <c r="K45" s="3">
         <v>23400</v>
       </c>
       <c r="L45" s="3">
+        <v>23400</v>
+      </c>
+      <c r="M45" s="3">
         <v>21900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>19100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3">
         <v>1000</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,62 +3094,65 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>737800</v>
+      </c>
+      <c r="E46" s="3">
         <v>857700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>951700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1055800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1138200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1224800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1013100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1084200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1104000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1177600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1242600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1318500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1382500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>430500</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3">
         <v>3800</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3063,19 +3165,22 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>59600</v>
-      </c>
-      <c r="E47" s="3">
-        <v>59600</v>
-      </c>
-      <c r="F47" s="3">
-        <v>59600</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -3086,39 +3191,39 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
         <v>72100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>27000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>20200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3">
         <v>690000</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3131,53 +3236,56 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>141200</v>
+      </c>
+      <c r="E48" s="3">
         <v>133500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>132200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>131700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>128100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>116500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>117100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>117300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>63000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>61000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>57900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>53200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>44000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>41600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3190,8 +3298,8 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3199,53 +3307,56 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>25300</v>
+        <v>83500</v>
       </c>
       <c r="E49" s="3">
-        <v>19000</v>
+        <v>84900</v>
       </c>
       <c r="F49" s="3">
-        <v>20600</v>
+        <v>78600</v>
       </c>
       <c r="G49" s="3">
-        <v>22000</v>
+        <v>80200</v>
       </c>
       <c r="H49" s="3">
-        <v>23600</v>
+        <v>81600</v>
       </c>
       <c r="I49" s="3">
-        <v>25100</v>
+        <v>83200</v>
       </c>
       <c r="J49" s="3">
+        <v>84700</v>
+      </c>
+      <c r="K49" s="3">
         <v>26600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>28200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>29600</v>
-      </c>
-      <c r="M49" s="3">
-        <v>25300</v>
       </c>
       <c r="N49" s="3">
         <v>25300</v>
       </c>
       <c r="O49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="P49" s="3">
         <v>18700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19700</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3258,8 +3369,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3267,8 +3378,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3449,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,8 +3520,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3418,38 +3538,38 @@
         <v>1800</v>
       </c>
       <c r="G52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I52" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K52" s="3">
+        <v>65000</v>
+      </c>
+      <c r="L52" s="3">
+        <v>6500</v>
+      </c>
+      <c r="M52" s="3">
+        <v>68000</v>
+      </c>
+      <c r="N52" s="3">
+        <v>70500</v>
+      </c>
+      <c r="O52" s="3">
+        <v>71100</v>
+      </c>
+      <c r="P52" s="3">
+        <v>66600</v>
+      </c>
+      <c r="Q52" s="3">
         <v>61300</v>
       </c>
-      <c r="H52" s="3">
-        <v>61900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>63400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>65000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>6500</v>
-      </c>
-      <c r="L52" s="3">
-        <v>68000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>70500</v>
-      </c>
-      <c r="N52" s="3">
-        <v>71100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>66600</v>
-      </c>
-      <c r="P52" s="3">
-        <v>61300</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3462,8 +3582,8 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3471,8 +3591,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,62 +3662,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>964300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1077800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1164400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1269400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1349600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1426700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1218700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1293000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1273800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1356300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1423300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1488400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1532000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>566100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3">
         <v>693700</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3733,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3762,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,62 +3789,63 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
         <v>5300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
-      </c>
-      <c r="N57" s="3">
-        <v>3600</v>
       </c>
       <c r="O57" s="3">
         <v>3600</v>
       </c>
       <c r="P57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q57" s="3">
         <v>5500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3">
         <v>700</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,31 +3858,34 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3759,21 +3893,21 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>700</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3786,8 +3920,8 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -3795,62 +3929,65 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>37800</v>
+        <v>6300</v>
       </c>
       <c r="E59" s="3">
-        <v>34500</v>
+        <v>5100</v>
       </c>
       <c r="F59" s="3">
-        <v>42100</v>
+        <v>6800</v>
       </c>
       <c r="G59" s="3">
-        <v>45200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>40000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>26400</v>
+        <v>6200</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K59" s="3">
         <v>22500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>28100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3">
         <v>300</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,62 +4000,65 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E60" s="3">
         <v>43200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>45100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>50000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>44100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12400</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3">
         <v>1100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,31 +4071,34 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>31200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>29900</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>30800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>22700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3967,17 +4110,17 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>1400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>78600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3999,62 +4142,65 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>140100</v>
+        <v>106300</v>
       </c>
       <c r="E62" s="3">
-        <v>151000</v>
+        <v>110200</v>
       </c>
       <c r="F62" s="3">
-        <v>189900</v>
+        <v>120000</v>
       </c>
       <c r="G62" s="3">
-        <v>190300</v>
+        <v>159200</v>
       </c>
       <c r="H62" s="3">
-        <v>298100</v>
+        <v>164300</v>
       </c>
       <c r="I62" s="3">
-        <v>118900</v>
+        <v>276100</v>
       </c>
       <c r="J62" s="3">
+        <v>96200</v>
+      </c>
+      <c r="K62" s="3">
         <v>98000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>84900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>97700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>140700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>156400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>218200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2800</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3">
         <v>24400</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,8 +4213,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4284,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4355,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,8 +4426,11 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4280,53 +4438,53 @@
         <v>183200</v>
       </c>
       <c r="E66" s="3">
+        <v>183200</v>
+      </c>
+      <c r="F66" s="3">
         <v>189200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>235100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>240300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>342200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>149200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>128200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>113700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>127700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>158900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>171600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>227300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>93800</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3">
         <v>25400</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4339,8 +4497,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4526,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4595,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4666,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4543,11 +4711,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>845900</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4569,8 +4737,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,62 +4808,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1609500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1465600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1342300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1247700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1132600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1134100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-848000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-734700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-667700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-588500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-538900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-476600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-481700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-402800</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3">
         <v>-200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,8 +4879,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +4950,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5021,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,62 +5092,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>781000</v>
+      </c>
+      <c r="E76" s="3">
         <v>894600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>975100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1034400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1109300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1084600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1069500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1164700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1160200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1228700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1264400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1316800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1304700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-373700</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3">
         <v>668300</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4977,8 +5163,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,67 +5234,70 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5118,62 +5310,65 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-143900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-123300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-94600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-115100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-286100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-113400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-66900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-79200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-49600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-62300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-78900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-65000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-41500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-33900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5186,8 +5381,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,64 +5410,65 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8700</v>
+        <v>6300</v>
       </c>
       <c r="E83" s="3">
-        <v>8500</v>
+        <v>5900</v>
       </c>
       <c r="F83" s="3">
-        <v>8100</v>
+        <v>5600</v>
       </c>
       <c r="G83" s="3">
-        <v>7800</v>
+        <v>5000</v>
       </c>
       <c r="H83" s="3">
-        <v>7500</v>
+        <v>4800</v>
       </c>
       <c r="I83" s="3">
-        <v>7100</v>
+        <v>4500</v>
       </c>
       <c r="J83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K83" s="3">
         <v>6600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5280,8 +5479,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5550,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5621,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5692,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5763,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,62 +5834,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-110300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-98800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-106600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-83300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-80200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-71700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-78600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-53100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-68300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-53100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-61400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-48700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-69500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-47900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-29700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-30300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5688,8 +5905,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,64 +5934,65 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-30500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5600</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -5782,8 +6003,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6074,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,62 +6145,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>88100</v>
+      </c>
+      <c r="E94" s="3">
         <v>158600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>12600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-196400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>177900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>117900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-54800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-49100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-50700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-476100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>21600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>42800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-690000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5986,8 +6216,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,31 +6245,32 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6080,8 +6314,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6385,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6456,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,62 +6527,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
         <v>4700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3400</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>284500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>60200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1020100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>75000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>693300</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6352,31 +6598,34 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6420,62 +6669,65 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E102" s="3">
         <v>64600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-93500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-276400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>97700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>330600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-97300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-47700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-117200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-103800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-537500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-60900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>972200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-72400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>39400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>12600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2800</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6486,6 +6738,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BB920E-7FF9-40AB-8CDA-826C469380AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9345"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JOBY" sheetId="6" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
   <si>
     <t>JOBY</t>
   </si>
@@ -303,7 +304,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -369,9 +370,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -409,9 +410,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -446,7 +447,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -481,7 +482,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -654,9 +655,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -675,21 +676,20 @@
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
@@ -744,23 +744,8 @@
       <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -815,23 +800,8 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -886,23 +856,8 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -957,23 +912,8 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -994,13 +934,8 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1055,23 +990,8 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1126,23 +1046,8 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-      <c r="U13" s="3">
-        <v>0</v>
-      </c>
-      <c r="V13" s="3">
-        <v>0</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0</v>
-      </c>
-      <c r="X13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1197,23 +1102,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1268,23 +1158,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1302,13 +1177,8 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1363,23 +1233,8 @@
       <c r="T17" s="3">
         <v>200</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1434,23 +1289,8 @@
       <c r="T18" s="3">
         <v>-200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1471,13 +1311,8 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1532,23 +1367,8 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1603,23 +1423,8 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1674,23 +1479,8 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1745,23 +1535,8 @@
       <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1816,23 +1591,8 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1887,23 +1647,8 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-      <c r="U25" s="3">
-        <v>0</v>
-      </c>
-      <c r="V25" s="3">
-        <v>0</v>
-      </c>
-      <c r="W25" s="3">
-        <v>0</v>
-      </c>
-      <c r="X25" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1958,23 +1703,8 @@
       <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2029,23 +1759,8 @@
       <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2100,23 +1815,8 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-      <c r="U28" s="3">
-        <v>0</v>
-      </c>
-      <c r="V28" s="3">
-        <v>0</v>
-      </c>
-      <c r="W28" s="3">
-        <v>0</v>
-      </c>
-      <c r="X28" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2171,23 +1871,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2242,23 +1927,8 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-      <c r="U30" s="3">
-        <v>0</v>
-      </c>
-      <c r="V30" s="3">
-        <v>0</v>
-      </c>
-      <c r="W30" s="3">
-        <v>0</v>
-      </c>
-      <c r="X30" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2313,23 +1983,8 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-      <c r="U31" s="3">
-        <v>0</v>
-      </c>
-      <c r="V31" s="3">
-        <v>0</v>
-      </c>
-      <c r="W31" s="3">
-        <v>0</v>
-      </c>
-      <c r="X31" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2384,23 +2039,8 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2455,23 +2095,8 @@
       <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2526,23 +2151,8 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-      <c r="U34" s="3">
-        <v>0</v>
-      </c>
-      <c r="V34" s="3">
-        <v>0</v>
-      </c>
-      <c r="W34" s="3">
-        <v>0</v>
-      </c>
-      <c r="X34" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2597,28 +2207,13 @@
       <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
@@ -2673,23 +2268,8 @@
       <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2710,13 +2290,8 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2737,13 +2312,8 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2798,23 +2368,8 @@
       <c r="T41" s="3">
         <v>2800</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2869,23 +2424,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2940,23 +2480,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3011,23 +2536,8 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
-      </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3">
-        <v>0</v>
-      </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3082,23 +2592,8 @@
       <c r="T45" s="3">
         <v>1000</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3153,23 +2648,8 @@
       <c r="T46" s="3">
         <v>3800</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3224,23 +2704,8 @@
       <c r="T47" s="3">
         <v>690000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3295,23 +2760,8 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
-      <c r="X48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3366,23 +2816,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3437,23 +2872,8 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-      <c r="U50" s="3">
-        <v>0</v>
-      </c>
-      <c r="V50" s="3">
-        <v>0</v>
-      </c>
-      <c r="W50" s="3">
-        <v>0</v>
-      </c>
-      <c r="X50" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3508,23 +2928,8 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-      <c r="U51" s="3">
-        <v>0</v>
-      </c>
-      <c r="V51" s="3">
-        <v>0</v>
-      </c>
-      <c r="W51" s="3">
-        <v>0</v>
-      </c>
-      <c r="X51" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3579,23 +2984,8 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3650,23 +3040,8 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-      <c r="U53" s="3">
-        <v>0</v>
-      </c>
-      <c r="V53" s="3">
-        <v>0</v>
-      </c>
-      <c r="W53" s="3">
-        <v>0</v>
-      </c>
-      <c r="X53" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3721,23 +3096,8 @@
       <c r="T54" s="3">
         <v>693700</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3758,13 +3118,8 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3785,13 +3140,8 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
-      <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3846,23 +3196,8 @@
       <c r="T57" s="3">
         <v>700</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3917,23 +3252,8 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3988,23 +3308,8 @@
       <c r="T59" s="3">
         <v>300</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4059,23 +3364,8 @@
       <c r="T60" s="3">
         <v>1100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4130,23 +3420,8 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4201,23 +3476,8 @@
       <c r="T62" s="3">
         <v>24400</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4272,23 +3532,8 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-      <c r="U63" s="3">
-        <v>0</v>
-      </c>
-      <c r="V63" s="3">
-        <v>0</v>
-      </c>
-      <c r="W63" s="3">
-        <v>0</v>
-      </c>
-      <c r="X63" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y63" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4343,23 +3588,8 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-      <c r="U64" s="3">
-        <v>0</v>
-      </c>
-      <c r="V64" s="3">
-        <v>0</v>
-      </c>
-      <c r="W64" s="3">
-        <v>0</v>
-      </c>
-      <c r="X64" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y64" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4414,23 +3644,8 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-      <c r="U65" s="3">
-        <v>0</v>
-      </c>
-      <c r="V65" s="3">
-        <v>0</v>
-      </c>
-      <c r="W65" s="3">
-        <v>0</v>
-      </c>
-      <c r="X65" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4485,23 +3700,8 @@
       <c r="T66" s="3">
         <v>25400</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4522,13 +3722,8 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-      <c r="U67" s="3"/>
-      <c r="V67" s="3"/>
-      <c r="W67" s="3"/>
-      <c r="X67" s="3"/>
-      <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4583,23 +3778,8 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-      <c r="U68" s="3">
-        <v>0</v>
-      </c>
-      <c r="V68" s="3">
-        <v>0</v>
-      </c>
-      <c r="W68" s="3">
-        <v>0</v>
-      </c>
-      <c r="X68" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4654,23 +3834,8 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-      <c r="U69" s="3">
-        <v>0</v>
-      </c>
-      <c r="V69" s="3">
-        <v>0</v>
-      </c>
-      <c r="W69" s="3">
-        <v>0</v>
-      </c>
-      <c r="X69" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y69" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4725,23 +3890,8 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4796,23 +3946,8 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-      <c r="U71" s="3">
-        <v>0</v>
-      </c>
-      <c r="V71" s="3">
-        <v>0</v>
-      </c>
-      <c r="W71" s="3">
-        <v>0</v>
-      </c>
-      <c r="X71" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4867,23 +4002,8 @@
       <c r="T72" s="3">
         <v>-200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4938,23 +4058,8 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-      <c r="U73" s="3">
-        <v>0</v>
-      </c>
-      <c r="V73" s="3">
-        <v>0</v>
-      </c>
-      <c r="W73" s="3">
-        <v>0</v>
-      </c>
-      <c r="X73" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5009,23 +4114,8 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-      <c r="U74" s="3">
-        <v>0</v>
-      </c>
-      <c r="V74" s="3">
-        <v>0</v>
-      </c>
-      <c r="W74" s="3">
-        <v>0</v>
-      </c>
-      <c r="X74" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y74" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5080,23 +4170,8 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-      <c r="U75" s="3">
-        <v>0</v>
-      </c>
-      <c r="V75" s="3">
-        <v>0</v>
-      </c>
-      <c r="W75" s="3">
-        <v>0</v>
-      </c>
-      <c r="X75" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -5151,23 +4226,8 @@
       <c r="T76" s="3">
         <v>668300</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5222,28 +4282,13 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-      <c r="U77" s="3">
-        <v>0</v>
-      </c>
-      <c r="V77" s="3">
-        <v>0</v>
-      </c>
-      <c r="W77" s="3">
-        <v>0</v>
-      </c>
-      <c r="X77" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y77" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
@@ -5298,23 +4343,8 @@
       <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5369,23 +4399,8 @@
       <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5406,13 +4421,8 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-      <c r="U82" s="3"/>
-      <c r="V82" s="3"/>
-      <c r="W82" s="3"/>
-      <c r="X82" s="3"/>
-      <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5467,23 +4477,8 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5538,23 +4533,8 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-      <c r="U84" s="3">
-        <v>0</v>
-      </c>
-      <c r="V84" s="3">
-        <v>0</v>
-      </c>
-      <c r="W84" s="3">
-        <v>0</v>
-      </c>
-      <c r="X84" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y84" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5609,23 +4589,8 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-      <c r="U85" s="3">
-        <v>0</v>
-      </c>
-      <c r="V85" s="3">
-        <v>0</v>
-      </c>
-      <c r="W85" s="3">
-        <v>0</v>
-      </c>
-      <c r="X85" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y85" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5680,23 +4645,8 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-      <c r="U86" s="3">
-        <v>0</v>
-      </c>
-      <c r="V86" s="3">
-        <v>0</v>
-      </c>
-      <c r="W86" s="3">
-        <v>0</v>
-      </c>
-      <c r="X86" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y86" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5751,23 +4701,8 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-      <c r="U87" s="3">
-        <v>0</v>
-      </c>
-      <c r="V87" s="3">
-        <v>0</v>
-      </c>
-      <c r="W87" s="3">
-        <v>0</v>
-      </c>
-      <c r="X87" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y87" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5822,23 +4757,8 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-      <c r="U88" s="3">
-        <v>0</v>
-      </c>
-      <c r="V88" s="3">
-        <v>0</v>
-      </c>
-      <c r="W88" s="3">
-        <v>0</v>
-      </c>
-      <c r="X88" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y88" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5893,23 +4813,8 @@
       <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5930,13 +4835,8 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-      <c r="U90" s="3"/>
-      <c r="V90" s="3"/>
-      <c r="W90" s="3"/>
-      <c r="X90" s="3"/>
-      <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5991,23 +4891,8 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6062,23 +4947,8 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-      <c r="U92" s="3">
-        <v>0</v>
-      </c>
-      <c r="V92" s="3">
-        <v>0</v>
-      </c>
-      <c r="W92" s="3">
-        <v>0</v>
-      </c>
-      <c r="X92" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y92" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6133,23 +5003,8 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-      <c r="U93" s="3">
-        <v>0</v>
-      </c>
-      <c r="V93" s="3">
-        <v>0</v>
-      </c>
-      <c r="W93" s="3">
-        <v>0</v>
-      </c>
-      <c r="X93" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y93" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6204,23 +5059,8 @@
       <c r="T94" s="3">
         <v>-690000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6241,13 +5081,8 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-      <c r="U95" s="3"/>
-      <c r="V95" s="3"/>
-      <c r="W95" s="3"/>
-      <c r="X95" s="3"/>
-      <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6302,23 +5137,8 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6373,23 +5193,8 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-      <c r="U97" s="3">
-        <v>0</v>
-      </c>
-      <c r="V97" s="3">
-        <v>0</v>
-      </c>
-      <c r="W97" s="3">
-        <v>0</v>
-      </c>
-      <c r="X97" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y97" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6444,23 +5249,8 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-      <c r="U98" s="3">
-        <v>0</v>
-      </c>
-      <c r="V98" s="3">
-        <v>0</v>
-      </c>
-      <c r="W98" s="3">
-        <v>0</v>
-      </c>
-      <c r="X98" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y98" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6515,23 +5305,8 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-      <c r="U99" s="3">
-        <v>0</v>
-      </c>
-      <c r="V99" s="3">
-        <v>0</v>
-      </c>
-      <c r="W99" s="3">
-        <v>0</v>
-      </c>
-      <c r="X99" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y99" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6586,23 +5361,8 @@
       <c r="T100" s="3">
         <v>693300</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6657,23 +5417,8 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6727,21 +5472,6 @@
       </c>
       <c r="T102" s="3">
         <v>2800</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BB920E-7FF9-40AB-8CDA-826C469380AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="JOBY" sheetId="6" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
   <si>
     <t>JOBY</t>
   </si>
@@ -304,7 +303,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -370,9 +369,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -410,9 +409,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -447,7 +446,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -482,7 +481,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -655,97 +654,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -759,11 +761,11 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>1000</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -779,8 +781,8 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -800,8 +802,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -815,11 +820,11 @@
         <v>0</v>
       </c>
       <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
         <v>200</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,8 +861,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -871,11 +879,11 @@
         <v>0</v>
       </c>
       <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>800</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -912,8 +920,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,64 +945,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>122400</v>
+      </c>
+      <c r="E12" s="3">
         <v>126100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>113000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>115600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>102100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>100600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>88800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>75500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>76100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>73900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>74200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>72100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>57300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>52100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>54000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>34200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>31800</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,13 +1061,16 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>53400</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1060,77 +1078,80 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>51900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9700</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E15" s="3">
         <v>8900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1158,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>149900</v>
+      </c>
+      <c r="E17" s="3">
         <v>156700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>144300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>145900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>129300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>128200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>116000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>99700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>101400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>97100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>99400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>94300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>77300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>77400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>68400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>45800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>40200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-149900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-156700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-144300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-145900</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-128200</v>
       </c>
       <c r="H18" s="3">
         <v>-128200</v>
       </c>
       <c r="I18" s="3">
+        <v>-128200</v>
+      </c>
+      <c r="J18" s="3">
         <v>-116000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-99700</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3">
         <v>-94300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-77300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-77400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-68400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-45800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-40200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,120 +1342,127 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-39000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-52200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-116100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>180700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>22000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3">
         <v>32100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>71800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6300</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-193600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-144000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-125800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-98400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-67900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-289200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-114700</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-57100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-74200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-60000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-37300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-31600</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1449,8 +1487,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1465,87 +1503,93 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-246700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-143300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-123300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-94600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-115100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-286000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-113400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-66900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-79200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-49500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-62300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-78900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-65000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-41500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-33900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -1556,17 +1600,17 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1574,11 +1618,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-10500</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1588,11 +1632,14 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-246300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-143900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-123300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-94600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-115100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-286100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-113400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-66900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-79200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-49600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-62300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-78900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-65000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-41500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-33900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-246300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-143900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-123300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-94600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-115100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-286100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-113400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-66900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-79200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-49600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-62300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-78900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-65000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-41500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-33900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,120 +2048,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-53200</v>
+      </c>
+      <c r="E32" s="3">
         <v>3800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>39000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>52200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>116100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-180700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-22000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3">
         <v>-32100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-71800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6300</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-246300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-143900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-123300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-94600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-115100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-286100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-113400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-66900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-79200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-49600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-62300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-78900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-65000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-41500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-33900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-246300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-143900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-123300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-94600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-115100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-286100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-113400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-66900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-79200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-49600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-62300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-78900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-65000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-41500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-33900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,176 +2396,186 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>199600</v>
+      </c>
+      <c r="E41" s="3">
         <v>152300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>175100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>110500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>204000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>480400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>382700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>146100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>193800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>311100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>417100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>955600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1016500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>44300</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>733200</v>
+      </c>
+      <c r="E42" s="3">
         <v>557700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>649900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>813300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>828200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>632100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>812100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>928000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>910700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>880700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>840400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>803700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>343200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>346000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>375200</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3900</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2506,8 +2600,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2536,120 +2630,129 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E45" s="3">
         <v>11200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>23400</v>
       </c>
       <c r="L45" s="3">
         <v>23400</v>
       </c>
       <c r="M45" s="3">
+        <v>23400</v>
+      </c>
+      <c r="N45" s="3">
         <v>21900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>969600</v>
+      </c>
+      <c r="E46" s="3">
         <v>737800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>857700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>951700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1055800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1138200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1224800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1013100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1084200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1104000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1177600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1242600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1318500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1382500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>430500</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2674,150 +2777,159 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>72100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>27000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>20300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>20200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3">
         <v>690000</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>149600</v>
+      </c>
+      <c r="E48" s="3">
         <v>141200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>133500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>132200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>131700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>128100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>116500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>117100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>117300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>63000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>61000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>57900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>53200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>44000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>41600</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>82100</v>
+      </c>
+      <c r="E49" s="3">
         <v>83500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>84900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>78600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>80200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>81600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>83200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>84700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>26600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>28200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>29600</v>
-      </c>
-      <c r="N49" s="3">
-        <v>25300</v>
       </c>
       <c r="O49" s="3">
         <v>25300</v>
       </c>
       <c r="P49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="Q49" s="3">
         <v>18700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19700</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,13 +3043,16 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="E52" s="3">
         <v>1800</v>
@@ -2946,46 +3064,49 @@
         <v>1800</v>
       </c>
       <c r="H52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I52" s="3">
         <v>1700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>65000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>68000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>70500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>71100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>66600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>61300</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1203500</v>
+      </c>
+      <c r="E54" s="3">
         <v>964300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1077800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1164400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1269400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1349600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1426700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1218700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1293000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1273800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1356300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1423300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1488400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1532000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>566100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3">
         <v>693700</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,259 +3268,272 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
-      </c>
-      <c r="O57" s="3">
-        <v>3600</v>
       </c>
       <c r="P57" s="3">
         <v>3600</v>
       </c>
       <c r="Q57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="R57" s="3">
         <v>5500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E58" s="3">
         <v>4800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>700</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E59" s="3">
         <v>6300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6200</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>2200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E60" s="3">
         <v>45800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>43200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>45100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>50000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>44100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12400</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T60" s="3">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E61" s="3">
         <v>31200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>29900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>30800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>26000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3403,81 +3544,87 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>1400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>78600</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>212900</v>
+      </c>
+      <c r="E62" s="3">
         <v>106300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>110200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>120000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>159200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>164300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>276100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>96200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>98000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>84900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>97700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>140700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>156400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>218200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2800</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>183200</v>
+        <v>291100</v>
       </c>
       <c r="E66" s="3">
         <v>183200</v>
       </c>
       <c r="F66" s="3">
+        <v>183200</v>
+      </c>
+      <c r="G66" s="3">
         <v>189200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>235100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>240300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>342200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>149200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>128200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>113700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>127700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>158900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>171600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>227300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>93800</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3879,19 +4045,22 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>845900</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,64 +4115,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1855700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1609500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1465600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1342300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1247700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1132600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1134100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-848000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-734700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-667700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-588500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-538900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-476600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-481700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-402800</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,64 +4351,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>912400</v>
+      </c>
+      <c r="E76" s="3">
         <v>781000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>894600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>975100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1034400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1109300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1084600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1069500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1164700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1160200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1228700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1264400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1316800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1304700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-373700</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T76" s="3">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3">
         <v>668300</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-246300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-143900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-123300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-94600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-115100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-286100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-113400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-66900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-79200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-49600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-62300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-78900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-65000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-41500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-33900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,64 +4617,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E83" s="3">
         <v>6300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2200</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-120500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-110300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-98800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-106600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-83300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-80200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-71700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-78600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-53100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-68300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-53100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-61400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-48700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-69500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-47900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-29700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-30300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,64 +5053,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-30500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5600</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,64 +5228,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-188600</v>
+      </c>
+      <c r="E94" s="3">
         <v>88100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>158600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>12600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-196400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>177900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>117900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-54800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-49100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-50700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-476100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>21600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>42800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-690000</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5107,8 +5339,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5137,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,64 +5546,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>356500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3400</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>284500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>60200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1020100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>75000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>693300</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5387,8 +5634,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5417,60 +5664,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-22800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>64600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-93500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-276400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>97700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>330600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-97300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-47700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-117200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-103800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-537500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-60900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>972200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-72400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>39400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>12600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
   <si>
     <t>JOBY</t>
   </si>
@@ -656,98 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -755,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -764,11 +768,11 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>1000</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -784,8 +788,8 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -805,13 +809,16 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
+      <c r="D9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -823,11 +830,11 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -864,13 +871,16 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
+      <c r="D10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -882,11 +892,11 @@
         <v>0</v>
       </c>
       <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -923,8 +933,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,67 +959,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E12" s="3">
         <v>122400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>126100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>113000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>115600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>102100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>100600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>88800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>75500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>76100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>73900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>74200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>72100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>57300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>52100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>54000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>34200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>31800</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,97 +1081,103 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>53400</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>51900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9700</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E15" s="3">
         <v>9500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>163300</v>
+      </c>
+      <c r="E17" s="3">
         <v>149900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>156700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>144300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>145900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>129300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>128200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>116000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>99700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>101400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>97100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>99400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>94300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>77300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>77400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>68400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>45800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>40200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-163300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-149900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-156700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-144300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-145900</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-128200</v>
       </c>
       <c r="I18" s="3">
         <v>-128200</v>
       </c>
       <c r="J18" s="3">
+        <v>-128200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-116000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-99700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3">
         <v>-94300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-77300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-77400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-68400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-45800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-40200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,126 +1376,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E20" s="3">
         <v>53200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-39000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-52200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-116100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>180700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>22000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>32100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>71800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>6300</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-83100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-193600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-144000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-125800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-98400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-67900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-289200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-114700</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-57100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-74200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-60000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-37300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-31600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1490,8 +1530,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1506,93 +1546,99 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-246700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-143300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-123300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-94600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-115100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-286000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-113400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-66900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-79200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-49500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-62300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-78900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-65000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-41500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-33900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -1603,17 +1649,17 @@
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1621,11 +1667,11 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1635,11 +1681,14 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-246300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-143900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-123300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-94600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-115100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-286100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-113400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-66900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-79200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-49600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-62300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-78900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-65000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-41500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-33900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-246300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-143900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-123300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-94600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-115100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-286100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-113400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-66900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-79200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-49600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-62300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-78900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-65000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-41500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-33900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-53200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>39000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>52200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>116100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-180700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-22000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>-32100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-71800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-6300</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-246300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-143900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-123300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-94600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-115100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-286100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-113400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-66900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-79200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-49600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-62300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-78900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-65000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-41500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-33900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-246300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-143900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-123300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-94600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-115100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-286100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-113400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-66900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-79200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-49600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-62300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-78900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-65000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-41500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-33900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,185 +2483,195 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E41" s="3">
         <v>199600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>152300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>175100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>110500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>204000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>480400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>382700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>49800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>146100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>193800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>311100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>417100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>955600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1016500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>44300</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>690200</v>
+      </c>
+      <c r="E42" s="3">
         <v>733200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>557700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>649900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>813300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>828200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>632100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>812100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>928000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>910700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>880700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>840400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>803700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>343200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>346000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>375200</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E43" s="3">
         <v>16000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3900</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2603,8 +2699,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2633,8 +2729,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2642,117 +2741,123 @@
         <v>14000</v>
       </c>
       <c r="E45" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F45" s="3">
         <v>11200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>16800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>23400</v>
       </c>
       <c r="M45" s="3">
         <v>23400</v>
       </c>
       <c r="N45" s="3">
+        <v>23400</v>
+      </c>
+      <c r="O45" s="3">
         <v>21900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>841500</v>
+      </c>
+      <c r="E46" s="3">
         <v>969600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>737800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>857700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>951700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1055800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1138200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1224800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1013100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1084200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1104000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1177600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1242600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1318500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1382500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>430500</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2780,156 +2885,165 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>72100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>27000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>20300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>20200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
         <v>690000</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>158800</v>
+      </c>
+      <c r="E48" s="3">
         <v>149600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>141200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>133500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>132200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>131700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>128100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>116500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>117100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>117300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>63000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>61000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>57900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>53200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>44000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>41600</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E49" s="3">
         <v>82100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>83500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>84900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>78600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>80200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>81600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>83200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>84700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>26600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>28200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>29600</v>
-      </c>
-      <c r="O49" s="3">
-        <v>25300</v>
       </c>
       <c r="P49" s="3">
         <v>25300</v>
       </c>
       <c r="Q49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="R49" s="3">
         <v>18700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>19700</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,16 +3163,19 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E52" s="3">
         <v>2200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1800</v>
       </c>
       <c r="F52" s="3">
         <v>1800</v>
@@ -3067,46 +3187,49 @@
         <v>1800</v>
       </c>
       <c r="I52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J52" s="3">
         <v>1700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>65000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>68000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>70500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>71100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>66600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>61300</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1084000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1203500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>964300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1077800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1164400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1269400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1349600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1426700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1218700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1293000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1273800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1356300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1423300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1488400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1532000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>566100</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3">
         <v>693700</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,274 +3399,287 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
         <v>4300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
-      </c>
-      <c r="P57" s="3">
-        <v>3600</v>
       </c>
       <c r="Q57" s="3">
         <v>3600</v>
       </c>
       <c r="R57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="S57" s="3">
         <v>5500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E58" s="3">
         <v>7600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>700</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E59" s="3">
         <v>6900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6200</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>2200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>28100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E60" s="3">
         <v>48100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>45800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>43200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>38200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>45100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>50000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>44100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12400</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E61" s="3">
         <v>30000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>31200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>29900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>30800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3547,84 +3690,90 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>1400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>78600</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>141900</v>
+      </c>
+      <c r="E62" s="3">
         <v>212900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>106300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>110200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>120000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>159200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>164300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>276100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>96200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>98000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>84900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>97700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>140700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>156400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>218200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2800</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>224600</v>
+      </c>
+      <c r="E66" s="3">
         <v>291100</v>
-      </c>
-      <c r="E66" s="3">
-        <v>183200</v>
       </c>
       <c r="F66" s="3">
         <v>183200</v>
       </c>
       <c r="G66" s="3">
+        <v>183200</v>
+      </c>
+      <c r="H66" s="3">
         <v>189200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>235100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>240300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>342200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>149200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>128200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>113700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>127700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>158900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>171600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>227300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>93800</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4048,19 +4216,22 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>845900</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1938100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1855700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1609500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1465600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1342300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1247700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1132600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1134100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-848000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-734700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-667700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-588500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-538900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-476600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-481700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-402800</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>859400</v>
+      </c>
+      <c r="E76" s="3">
         <v>912400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>781000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>894600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>975100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1034400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1109300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1084600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1069500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1164700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1160200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1228700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1264400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1316800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1304700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-373700</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3">
         <v>668300</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-246300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-143900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-123300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-94600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-115100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-286100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-113400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-66900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-79200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-49600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-62300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-78900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-65000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-41500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-33900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,67 +4816,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E83" s="3">
         <v>6600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-111000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-120500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-110300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-98800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-106600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-83300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-80200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-71700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-78600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-53100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-68300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-53100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-61400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-48700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-69500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-47900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-29700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-30300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,67 +5274,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-30500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5600</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,67 +5458,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-188600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>88100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>158600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>12600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-196400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>177900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>117900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-54800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-49100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-50700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-476100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>21600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-23100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>42800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-690000</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5342,8 +5576,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,67 +5792,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E100" s="3">
         <v>356500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3400</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>284500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>60200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1020100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>75000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>693300</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5637,8 +5886,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5667,63 +5916,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-77300</v>
+      </c>
+      <c r="E102" s="3">
         <v>47300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-22800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>64600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-93500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-276400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>97700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>330600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-97300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-47700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-117200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-103800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-537500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-60900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>972200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-72400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>39400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>12600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>JOBY</t>
   </si>
@@ -656,114 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
@@ -771,11 +775,11 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>1000</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -791,8 +795,8 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -812,16 +816,19 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -833,11 +840,11 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
@@ -874,16 +881,19 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -895,11 +905,11 @@
         <v>0</v>
       </c>
       <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>800</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>136400</v>
+      </c>
+      <c r="E12" s="3">
         <v>134300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>122400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>126100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>113000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>115600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>102100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>100600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>88800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>75500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>76100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>73900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>74200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>72100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>57300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>52100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>54000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>34200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>31800</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,103 +1101,109 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>53400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>51900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9700</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E15" s="3">
         <v>9100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7100</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>167900</v>
+      </c>
+      <c r="E17" s="3">
         <v>163300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>149900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>156700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>144300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>145900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>129300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>128200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>116000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>99700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>101400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>97100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>99400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>94300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>77300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>77400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>68400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>45800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>40200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-167900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-163300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-149900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-156700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-144300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-145900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-128200</v>
       </c>
       <c r="J18" s="3">
         <v>-128200</v>
       </c>
       <c r="K18" s="3">
+        <v>-128200</v>
+      </c>
+      <c r="L18" s="3">
         <v>-116000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-99700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-94300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-77300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-77400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-68400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-45800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-40200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,132 +1410,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>166600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-71000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>53200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-39000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-52200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-116100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>180700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>22000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>32100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>71800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6300</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-324700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-83100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-193600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-144000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-125800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-98400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-67900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-289200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-114700</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-57100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-74200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-60000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-37300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-31600</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1533,8 +1573,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1549,99 +1589,105 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-324600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-82400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-246700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-143300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-123300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-94600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-115100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-286000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-113400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-66900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-79200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-49500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-62300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-78900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-65000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-41500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-33900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
@@ -1652,17 +1698,17 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1670,11 +1716,11 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-10500</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1684,11 +1730,14 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-324700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-82400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-246300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-143900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-123300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-94600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-115100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-286100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-113400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-66900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-79200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-49600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-62300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-78900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-65000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-41500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-33900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-324700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-82400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-246300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-143900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-123300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-94600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-115100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-286100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-113400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-66900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-79200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-49600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-62300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-78900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-65000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-41500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-33900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-166600</v>
+      </c>
+      <c r="E32" s="3">
         <v>71000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-53200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>39000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>52200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>116100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-180700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-22000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-32100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-71800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6300</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-324700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-82400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-246300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-143900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-123300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-94600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-115100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-286100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-113400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-66900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-79200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-49600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-62300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-78900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-65000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-41500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-33900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-324700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-82400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-246300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-143900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-123300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-94600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-115100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-286100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-113400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-66900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-79200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-49600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-62300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-78900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-65000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-41500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-33900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,194 +2570,204 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>336300</v>
+      </c>
+      <c r="E41" s="3">
         <v>122300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>199600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>152300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>175100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>110500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>204000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>480400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>382700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>49800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>146100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>193800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>311100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>417100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>955600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1016500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>44300</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>654700</v>
+      </c>
+      <c r="E42" s="3">
         <v>690200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>733200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>557700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>649900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>813300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>828200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>632100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>812100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>928000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>910700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>880700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>840400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>803700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>343200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>346000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>375200</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E43" s="3">
         <v>9800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3900</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2702,8 +2798,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2732,132 +2828,141 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>14000</v>
+        <v>15300</v>
       </c>
       <c r="E45" s="3">
         <v>14000</v>
       </c>
       <c r="F45" s="3">
+        <v>14000</v>
+      </c>
+      <c r="G45" s="3">
         <v>11200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>16800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>23400</v>
       </c>
       <c r="N45" s="3">
         <v>23400</v>
       </c>
       <c r="O45" s="3">
+        <v>23400</v>
+      </c>
+      <c r="P45" s="3">
         <v>21900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>19100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1014500</v>
+      </c>
+      <c r="E46" s="3">
         <v>841500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>969600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>737800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>857700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>951700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1055800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1138200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1224800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1013100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1084200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1104000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1177600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1242600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1318500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1382500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>430500</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2888,162 +2993,171 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>72100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>20100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>27000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>20300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>20200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3">
         <v>690000</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>163300</v>
+      </c>
+      <c r="E48" s="3">
         <v>158800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>149600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>141200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>133500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>132200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>131700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>128100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>116500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>117100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>117300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>63000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>61000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>57900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>53200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>44000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>41600</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>79600</v>
+      </c>
+      <c r="E49" s="3">
         <v>80800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>82100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>83500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>84900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>78600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>80200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>81600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>83200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>84700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>26600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>28200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>29600</v>
-      </c>
-      <c r="P49" s="3">
-        <v>25300</v>
       </c>
       <c r="Q49" s="3">
         <v>25300</v>
       </c>
       <c r="R49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="S49" s="3">
         <v>18700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19700</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,19 +3283,22 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E52" s="3">
         <v>2900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1800</v>
       </c>
       <c r="G52" s="3">
         <v>1800</v>
@@ -3190,46 +3310,49 @@
         <v>1800</v>
       </c>
       <c r="J52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K52" s="3">
         <v>1700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>65000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>68000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>70500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>71100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>66600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>61300</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1259900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1084000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1203500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>964300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1077800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1164400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1269400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1349600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1426700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1218700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1293000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1273800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1356300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1423300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1488400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1532000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>566100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3">
         <v>693700</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,289 +3530,302 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2700</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>3600</v>
       </c>
       <c r="R57" s="3">
         <v>3600</v>
       </c>
       <c r="S57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="T57" s="3">
         <v>5500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E58" s="3">
         <v>5400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3500</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>1000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>700</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6200</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>2200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>28100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6200</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E60" s="3">
         <v>47500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>48100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>45800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>43200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>38200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>45100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>50000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>44100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>28800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12400</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E61" s="3">
         <v>35200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>30000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>29900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>31000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>30800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3693,87 +3836,93 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>1400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>78600</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>268100</v>
+      </c>
+      <c r="E62" s="3">
         <v>141900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>212900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>106300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>110200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>120000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>159200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>164300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>276100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>96200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>98000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>84900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>97700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>140700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>156400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>218200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2800</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>361600</v>
+      </c>
+      <c r="E66" s="3">
         <v>224600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>291100</v>
-      </c>
-      <c r="F66" s="3">
-        <v>183200</v>
       </c>
       <c r="G66" s="3">
         <v>183200</v>
       </c>
       <c r="H66" s="3">
+        <v>183200</v>
+      </c>
+      <c r="I66" s="3">
         <v>189200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>235100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>240300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>342200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>149200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>128200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>113700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>127700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>158900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>171600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>227300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>93800</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4219,19 +4387,22 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>845900</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2262800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1938100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1855700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1609500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1465600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1342300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1247700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1132600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1134100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-848000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-734700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-667700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-588500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-538900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-476600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-481700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-402800</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>898300</v>
+      </c>
+      <c r="E76" s="3">
         <v>859400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>912400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>781000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>894600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>975100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1034400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1109300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1084600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1069500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1164700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1160200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1228700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1264400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1316800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1304700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-373700</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3">
         <v>668300</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-324700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-82400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-246300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-143900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-123300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-94600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-115100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-286100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-113400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-66900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-79200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-49600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-62300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-78900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-65000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-41500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-33900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,70 +5015,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E83" s="3">
         <v>7000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2200</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-106600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-111000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-120500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-110300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-98800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-106600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-83300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-80200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-71700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-78600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-53100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-68300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-53100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-61400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-48700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-69500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-47900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-29700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-30300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,70 +5495,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-30500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5600</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E94" s="3">
         <v>31600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-188600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>88100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>158600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>12600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-196400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>177900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>117900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-54800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-49100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-50700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-476100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>21600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-23100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>42800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-690000</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5579,8 +5813,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,70 +6038,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>296000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>356500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3400</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>284500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>60200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1020100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>75000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>693300</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5889,8 +6138,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5919,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-77300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>47300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-22800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>64600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-93500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-276400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>97700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>330600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-97300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-47700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-117200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-103800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-537500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-60900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>972200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-72400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>39400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>12600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>JOBY</t>
   </si>
@@ -656,128 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E8" s="3">
         <v>22600</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
@@ -785,11 +788,11 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>1000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -805,8 +808,8 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -826,22 +829,25 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E9" s="3">
         <v>10100</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
@@ -853,11 +859,11 @@
         <v>0</v>
       </c>
       <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -894,22 +900,25 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E10" s="3">
         <v>12500</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -921,11 +930,11 @@
         <v>0</v>
       </c>
       <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -962,8 +971,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,76 +1000,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>161300</v>
+      </c>
+      <c r="E12" s="3">
         <v>149200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>136400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>134300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>122400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>126100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>113000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>115600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>102100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>100600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>88800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>75500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>76100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>73900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>74200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>72100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>57300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>52100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>54000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>34200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>31800</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,25 +1140,28 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5800</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>53400</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>21400</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1150,89 +1169,92 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>51900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>9700</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E15" s="3">
         <v>10200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7100</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1260,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>204200</v>
+        <v>243400</v>
       </c>
       <c r="E17" s="3">
+        <v>198400</v>
+      </c>
+      <c r="F17" s="3">
         <v>167900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>163300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>149900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>156700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>144300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>145900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>129300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>128200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>116000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>99700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>101400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>97100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>99400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>94300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>77300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>77400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>68400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>45800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>40200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-181700</v>
+        <v>-212600</v>
       </c>
       <c r="E18" s="3">
+        <v>-175900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-167900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-163300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-149900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-156700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-144300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-145900</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-128200</v>
       </c>
       <c r="L18" s="3">
         <v>-128200</v>
       </c>
       <c r="M18" s="3">
+        <v>-128200</v>
+      </c>
+      <c r="N18" s="3">
         <v>-116000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-99700</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-94300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-77300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-77400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-68400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-45800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-40200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,144 +1477,151 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-81400</v>
+      </c>
+      <c r="E20" s="3">
         <v>229100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>166600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-71000</v>
       </c>
-      <c r="G20" s="3">
-        <v>53200</v>
-      </c>
       <c r="H20" s="3">
+        <v>85300</v>
+      </c>
+      <c r="I20" s="3">
         <v>-3800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-39000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-52200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-116100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>180700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>22000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
         <v>32100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>71800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>6300</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-400600</v>
+        <v>-120100</v>
       </c>
       <c r="E21" s="3">
+        <v>-394800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-324700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-83100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-193600</v>
-      </c>
       <c r="H21" s="3">
+        <v>-225700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-144000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-125800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-98400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-67900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-289200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-114700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-57100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-74200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-60000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-37300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-31600</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1619,8 +1658,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1635,111 +1674,117 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-120500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-401100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-324600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-82400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-246700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-143300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-123300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-94600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-115100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-286000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-113400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-66900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-79200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-49500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-62300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-78900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-65000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-41500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-33900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1750,17 +1795,17 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1768,11 +1813,11 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-10500</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -1782,11 +1827,14 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-121500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-401200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-324700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-82400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-246300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-143900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-123300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-94600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-115100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-286100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-113400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-66900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-79200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-49600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-62300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-78900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-65000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-41500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-33900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-121500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-401200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-324700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-82400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-246300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-143900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-123300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-94600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-115100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-286100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-113400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-66900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-79200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-49600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-62300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-78900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-65000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-41500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-33900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2327,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>81400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-229100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-166600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>71000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-53200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-85300</v>
+      </c>
+      <c r="I32" s="3">
         <v>3800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>39000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>52200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>116100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-180700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-22000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
         <v>-32100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-71800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-6300</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-121500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-401200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-324700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-82400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-246300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-143900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-123300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-94600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-115100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-286100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-113400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-66900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-79200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-49600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-62300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-78900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-65000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-41500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-33900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-121500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-401200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-324700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-82400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-246300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-143900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-123300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-94600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-115100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-286100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-113400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-66900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-79200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-49600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-62300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-78900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-65000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-41500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-33900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,212 +2743,222 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>240800</v>
+      </c>
+      <c r="E41" s="3">
         <v>208400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>336300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>122300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>199600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>152300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>175100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>110500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>204000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>480400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>382700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>49800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>146100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>193800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>311100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>417100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>955600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1016500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>44300</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X41" s="3">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1167100</v>
+      </c>
+      <c r="E42" s="3">
         <v>769800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>654700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>690200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>733200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>557700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>649900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>813300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>828200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>632100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>812100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>928000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>910700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>880700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>840400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>803700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>343200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>346000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>375200</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E43" s="3">
         <v>10400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3900</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2900,8 +2995,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2930,144 +3025,153 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E45" s="3">
         <v>20600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>14000</v>
       </c>
       <c r="G45" s="3">
         <v>14000</v>
       </c>
       <c r="H45" s="3">
+        <v>14000</v>
+      </c>
+      <c r="I45" s="3">
         <v>11200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>16800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>23400</v>
       </c>
       <c r="P45" s="3">
         <v>23400</v>
       </c>
       <c r="Q45" s="3">
+        <v>23400</v>
+      </c>
+      <c r="R45" s="3">
         <v>21900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>19100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7100</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1445800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1018600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1014500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>841500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>969600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>737800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>857700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>951700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1055800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1138200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1224800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1013100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1084200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1104000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1177600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1242600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1318500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1382500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>430500</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X46" s="3">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3104,174 +3208,183 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>72100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>20100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>27000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>20300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>20200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13100</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="3">
         <v>690000</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>178400</v>
+      </c>
+      <c r="E48" s="3">
         <v>173800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>163300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>158800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>149600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>141200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>133500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>132200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>131700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>128100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>116500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>117100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>117300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>63000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>61000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>57900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>53200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>44000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>41600</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>167900</v>
+      </c>
+      <c r="E49" s="3">
         <v>171000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>79600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>80800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>82100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>83500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>84900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>78600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>80200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>81600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>83200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>84700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>26600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>28200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>29600</v>
-      </c>
-      <c r="R49" s="3">
-        <v>25300</v>
       </c>
       <c r="S49" s="3">
         <v>25300</v>
       </c>
       <c r="T49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="U49" s="3">
         <v>18700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>19700</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,25 +3522,28 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1800</v>
       </c>
       <c r="I52" s="3">
         <v>1800</v>
@@ -3436,46 +3555,49 @@
         <v>1800</v>
       </c>
       <c r="L52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M52" s="3">
         <v>1700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>65000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>68000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>70500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>71100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>66600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>61300</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3664,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1795100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1366300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1259900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1084000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1203500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>964300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1077800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1164400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1269400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1349600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1426700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1218700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1293000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1273800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1356300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1423300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1488400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1532000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>566100</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X54" s="3">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3">
         <v>693700</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,319 +3791,332 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E57" s="3">
         <v>13400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2700</v>
-      </c>
-      <c r="S57" s="3">
-        <v>3600</v>
       </c>
       <c r="T57" s="3">
         <v>3600</v>
       </c>
       <c r="U57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="V57" s="3">
         <v>5500</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E58" s="3">
         <v>10600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3500</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
         <v>1000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>700</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="E59" s="3">
         <v>6000</v>
       </c>
       <c r="F59" s="3">
+        <v>6000</v>
+      </c>
+      <c r="G59" s="3">
         <v>6300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3">
         <v>2200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>28100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6200</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E60" s="3">
         <v>74900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>58900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>47500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>48100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>45800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>43200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>38200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>45100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>50000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>44100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>30000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12400</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X60" s="3">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E61" s="3">
         <v>35000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>34600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>35200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>30000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>31200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>29900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>26000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>22000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3985,93 +4127,99 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>1400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>78600</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>291700</v>
+      </c>
+      <c r="E62" s="3">
         <v>360000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>268100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>141900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>212900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>106300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>110200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>120000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>159200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>164300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>276100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>96200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>98000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>84900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>97700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>140700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>156400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>218200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2800</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X62" s="3">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4428,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>385400</v>
+      </c>
+      <c r="E66" s="3">
         <v>469900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>361600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>224600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>291100</v>
-      </c>
-      <c r="H66" s="3">
-        <v>183200</v>
       </c>
       <c r="I66" s="3">
         <v>183200</v>
       </c>
       <c r="J66" s="3">
+        <v>183200</v>
+      </c>
+      <c r="K66" s="3">
         <v>189200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>235100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>240300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>342200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>149200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>128200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>113700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>127700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>158900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>171600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>227300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>93800</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X66" s="3">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4561,19 +4728,22 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>845900</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4810,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2785600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2664000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2262800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1938100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1855700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1609500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1465600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1342300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1247700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1132600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1134100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-848000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-734700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-667700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-588500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-538900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-476600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-481700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-402800</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5094,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1409700</v>
+      </c>
+      <c r="E76" s="3">
         <v>896500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>898300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>859400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>912400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>781000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>894600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>975100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1034400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1109300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1084600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1069500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1164700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1160200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1228700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1264400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1316800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1304700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-373700</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X76" s="3">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3">
         <v>668300</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-121500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-401200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-324700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-82400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-246300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-143900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-123300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-94600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-115100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-286100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-113400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-66900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-79200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-49600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-62300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-78900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-65000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-41500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-33900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,76 +5412,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E83" s="3">
         <v>7500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2200</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-153200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-139200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-106600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-111000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-120500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-110300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-98800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-106600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-83300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-80200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-71700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-78600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-53100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-68300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-53100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-61400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-48700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-69500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-47900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-29700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-30300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5936,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-30500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5600</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6147,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-408500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-123100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>24600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>31600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-188600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>88100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>158600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>12600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-196400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>177900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>117900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-54800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-49100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-50700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-476100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>21600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-23100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>42800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-690000</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6053,8 +6286,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6083,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,76 +6529,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>594000</v>
+      </c>
+      <c r="E100" s="3">
         <v>134700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>296000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>356500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>284500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>60200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1020100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>75000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>693300</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6393,8 +6641,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6423,72 +6671,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-127600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>214000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-77300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>47300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-22800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>64600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-93500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-276400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>97700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>330600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-97300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-47700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-117200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-103800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-537500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-60900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>972200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-72400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>39400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>12600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JOBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
   <si>
     <t>JOBY</t>
   </si>
@@ -656,134 +656,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E8" s="3">
         <v>30800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22600</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
@@ -791,11 +795,11 @@
         <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>1000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,8 +815,8 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -832,25 +836,28 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E9" s="3">
         <v>19300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10100</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
@@ -862,11 +869,11 @@
         <v>0</v>
       </c>
       <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,25 +910,28 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E10" s="3">
         <v>11600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12500</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
@@ -933,11 +943,11 @@
         <v>0</v>
       </c>
       <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
         <v>800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -974,8 +984,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,79 +1014,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>177500</v>
+      </c>
+      <c r="E12" s="3">
         <v>161300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>149200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>136400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>134300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>122400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>126100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>113000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>115600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>102100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>100600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>88800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>75500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>76100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>73900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>74200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>72100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>57300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>52100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>54000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>34200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>31800</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,121 +1160,127 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-68500</v>
+      </c>
+      <c r="E14" s="3">
         <v>3100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>-36800</v>
+      </c>
+      <c r="I14" s="3">
         <v>21400</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>51900</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>9700</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E15" s="3">
         <v>11100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>7100</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1285,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>257800</v>
+      </c>
+      <c r="E17" s="3">
         <v>243400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>198400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>167900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>163300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>149900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>156700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>144300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>145900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>129300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>128200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>116000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>99700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>101400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>97100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>99400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>94300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>77300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>77400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>68400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>45800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>40200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-233600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-212600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-175900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-167900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-163300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-149900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-156700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-144300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-145900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-128200</v>
       </c>
       <c r="M18" s="3">
         <v>-128200</v>
       </c>
       <c r="N18" s="3">
+        <v>-128200</v>
+      </c>
+      <c r="O18" s="3">
         <v>-116000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-99700</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>-94300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-77300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-77400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-68400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-45800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-40200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,150 +1511,157 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-81400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>229100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>166600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-71000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="I20" s="3">
         <v>85300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-39000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-52200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-116100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>180700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>22000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3">
         <v>32100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>71800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>6300</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-185000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-120100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-394800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-324700</v>
       </c>
-      <c r="G21" s="3">
-        <v>-83100</v>
-      </c>
       <c r="H21" s="3">
+        <v>-119900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-225700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-144000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-125800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-98400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-67900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-289200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-114700</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-57100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-74200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-60000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-37300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-31600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1661,8 +1701,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1677,117 +1717,123 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-109800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-120500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-401100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-324600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-82400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-246700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-143300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-123300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-94600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-115100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-286000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-113400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-66900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-79200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-49500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-62300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-78900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-65000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-41500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-33900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1798,17 +1844,17 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1816,11 +1862,11 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-10500</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -1830,11 +1876,14 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-121500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-401200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-324700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-82400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-246300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-143900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-123300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-94600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-115100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-286100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-113400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-66900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-79200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-49600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-62300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-78900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-65000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-41500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-33900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-121500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-401200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-324700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-82400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-246300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-143900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-123300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-94600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-115100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-286100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-113400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-66900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-79200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-49600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-62300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-78900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-65000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-41500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-33900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,150 +2397,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E32" s="3">
         <v>81400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-229100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-166600</v>
       </c>
-      <c r="G32" s="3">
-        <v>71000</v>
-      </c>
       <c r="H32" s="3">
+        <v>34200</v>
+      </c>
+      <c r="I32" s="3">
         <v>-85300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>39000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>52200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>116100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-180700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-22000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3">
         <v>-32100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-71800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-121500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-401200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-324700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-82400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-246300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-143900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-123300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-94600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-115100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-286100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-113400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-66900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-79200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-49600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-62300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-78900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-65000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-41500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-33900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-121500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-401200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-324700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-82400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-246300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-143900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-123300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-94600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-115100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-286100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-113400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-66900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-79200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-49600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-62300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-78900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-65000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-41500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-33900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,221 +2830,231 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>874500</v>
+      </c>
+      <c r="E41" s="3">
         <v>240800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>208400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>336300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>122300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>199600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>152300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>175100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>110500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>204000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>480400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>382700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>49800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>146100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>193800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>311100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>417100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>955600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1016500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>44300</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1591700</v>
+      </c>
+      <c r="E42" s="3">
         <v>1167100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>769800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>654700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>690200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>733200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>557700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>649900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>813300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>828200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>632100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>812100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>928000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>910700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>880700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>840400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>803700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>343200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>346000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>375200</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E43" s="3">
         <v>7100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3900</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2998,8 +3094,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3028,150 +3124,159 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E45" s="3">
         <v>21200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>14000</v>
       </c>
       <c r="H45" s="3">
         <v>14000</v>
       </c>
       <c r="I45" s="3">
+        <v>14000</v>
+      </c>
+      <c r="J45" s="3">
         <v>11200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>23400</v>
       </c>
       <c r="Q45" s="3">
         <v>23400</v>
       </c>
       <c r="R45" s="3">
+        <v>23400</v>
+      </c>
+      <c r="S45" s="3">
         <v>21900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>19100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2511600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1445800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1018600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1014500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>841500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>969600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>737800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>857700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>951700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1055800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1138200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1224800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1013100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1084200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1104000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1177600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1242600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1318500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1382500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>430500</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3211,180 +3316,189 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>72100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>20100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>27000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>20300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>20200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13100</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z47" s="3">
         <v>690000</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>242900</v>
+      </c>
+      <c r="E48" s="3">
         <v>178400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>173800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>163300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>158800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>149600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>141200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>133500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>132200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>131700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>128100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>116500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>117100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>117300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>63000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>61000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>57900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>53200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>44000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>41600</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>169400</v>
+      </c>
+      <c r="E49" s="3">
         <v>167900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>171000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>79600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>80800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>82100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>83500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>84900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>78600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>80200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>81600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>83200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>84700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>26600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>28200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>29600</v>
-      </c>
-      <c r="S49" s="3">
-        <v>25300</v>
       </c>
       <c r="T49" s="3">
         <v>25300</v>
       </c>
       <c r="U49" s="3">
+        <v>25300</v>
+      </c>
+      <c r="V49" s="3">
         <v>18700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>19700</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,28 +3642,31 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E52" s="3">
         <v>3000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1800</v>
       </c>
       <c r="J52" s="3">
         <v>1800</v>
@@ -3558,46 +3678,49 @@
         <v>1800</v>
       </c>
       <c r="M52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N52" s="3">
         <v>1700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>65000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>68000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>70500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>71100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>66600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>61300</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2927700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1795100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1366300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1259900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1084000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1203500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>964300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1077800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1164400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1269400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1349600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1426700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1218700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1293000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1273800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1356300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1423300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1488400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1532000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>566100</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3">
         <v>693700</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,334 +3922,347 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E57" s="3">
         <v>3600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2700</v>
-      </c>
-      <c r="T57" s="3">
-        <v>3600</v>
       </c>
       <c r="U57" s="3">
         <v>3600</v>
       </c>
       <c r="V57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="W57" s="3">
         <v>5500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E58" s="3">
         <v>10700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3500</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
         <v>1000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>700</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E59" s="3">
         <v>7000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>6000</v>
       </c>
       <c r="F59" s="3">
         <v>6000</v>
       </c>
       <c r="G59" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H59" s="3">
         <v>6300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>2200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>24500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>28100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6200</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>113900</v>
+      </c>
+      <c r="E60" s="3">
         <v>60000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>74900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>58900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>48100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>45800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>38200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>45100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>50000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>44100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>28800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>30000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>18200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12400</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>735400</v>
+      </c>
+      <c r="E61" s="3">
         <v>33600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>35000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>34600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>35200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>30000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>31200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>29900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>30800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4130,96 +4273,102 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>1400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>78600</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E62" s="3">
         <v>291700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>360000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>268100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>141900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>212900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>106300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>110200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>120000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>159200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>164300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>276100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>96200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>98000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>84900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>97700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>140700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>156400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>218200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2800</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3">
         <v>24400</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>969900</v>
+      </c>
+      <c r="E66" s="3">
         <v>385400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>469900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>361600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>224600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>291100</v>
-      </c>
-      <c r="I66" s="3">
-        <v>183200</v>
       </c>
       <c r="J66" s="3">
         <v>183200</v>
       </c>
       <c r="K66" s="3">
+        <v>183200</v>
+      </c>
+      <c r="L66" s="3">
         <v>189200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>235100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>240300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>342200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>149200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>128200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>113700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>127700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>158900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>171600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>227300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>93800</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4731,19 +4899,22 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>845900</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,79 +4984,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2895500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2785600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2664000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2262800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1938100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1855700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1609500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1465600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1342300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1247700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1132600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1134100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-848000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-734700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-667700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-588500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-538900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-476600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-481700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-402800</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1957700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1409700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>896500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>898300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>859400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>912400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>781000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>894600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>975100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1034400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1109300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1084600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1069500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1164700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1160200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1228700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1264400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1316800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1304700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-373700</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3">
         <v>668300</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-121500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-401200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-324700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-82400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-246300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-143900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-123300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-94600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-115100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-286100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-113400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-66900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-79200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-49600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-62300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-78900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-65000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-41500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-33900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,79 +5611,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E83" s="3">
         <v>8000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2200</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-144400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-153200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-139200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-106600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-111000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-120500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-110300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-98800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-106600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-83300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-80200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-71700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-78600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-53100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-68300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-53100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-61400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-48700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-69500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-47900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-29700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-30300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,79 +6157,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-77900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-505500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-408500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-123100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>24600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>31600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-188600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>88100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>158600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>12600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-196400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>177900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>117900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-54800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-49100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-50700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-476100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>21600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-23100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>42800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-690000</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6289,8 +6523,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,79 +6775,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1283600</v>
+      </c>
+      <c r="E100" s="3">
         <v>594000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>134700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>296000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>356500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3400</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>284500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>60200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1020100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>75000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>693300</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6644,8 +6893,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6674,75 +6923,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>633700</v>
+      </c>
+      <c r="E102" s="3">
         <v>32300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-127600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>214000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-77300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>47300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-22800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>64600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-93500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-276400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>97700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>330600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-97300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-47700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-117200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-103800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-537500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-60900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>972200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-72400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>39400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>12600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2800</v>
       </c>
     </row>
